--- a/docs/downloads/05/tbl_house_status_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/05/tbl_house_status_alaotra_ambatoharanana.xlsx
@@ -405,12 +405,6 @@
           <t>Prêtée</t>
         </is>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
